--- a/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
+++ b/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
@@ -41,7 +41,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
     <xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
     <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyAlignment="1">
@@ -53,6 +53,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -64,7 +65,7 @@
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="5" max="5" width="17" style="5" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
@@ -224,5 +225,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G5"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G5">
+      <formula1>"Full Time,Part Time,Contract,Terminated"</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
 </file>
--- a/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
+++ b/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
@@ -225,8 +225,14 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G5"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G2:G5">
+  <dataValidations count="3">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" sqref="A2:A5">
+      <formula1>ISNUMBER(A2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F5">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G5">
       <formula1>"Full Time,Part Time,Contract,Terminated"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
+++ b/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
@@ -226,13 +226,13 @@
   </sheetData>
   <autoFilter ref="A1:G5"/>
   <dataValidations count="3">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" sqref="A2:A5">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="A2:A5">
       <formula1>ISNUMBER(A2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F5">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="F2:F5">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G5">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." sqref="G2:G5">
       <formula1>"Full Time,Part Time,Contract,Terminated"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
+++ b/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
@@ -55,6 +55,15 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0"/>
   </cellXfs>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -225,9 +234,30 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G5"/>
-  <dataValidations count="3">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="A2:A5">
+  <conditionalFormatting sqref="A2:A5">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(A2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B5">
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(B2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C5">
+    <cfRule type="containsBlanks" dxfId="0" priority="3">
+      <formula>LEN(TRIM(C2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="5">
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="A2:A5">
       <formula1>ISNUMBER(A2)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="B2:B5">
+      <formula1>LEN(TRIM(B2))&gt;0</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="C2:C5">
+      <formula1>LEN(TRIM(C2))&gt;0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="F2:F5">
       <formula1>"TRUE,FALSE"</formula1>

--- a/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
+++ b/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -267,4 +267,18 @@
     </dataValidation>
   </dataValidations>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Sheet1">
+    <column index="1" property="Id"/>
+    <column index="2" property="Name"/>
+    <column index="3" property="Email"/>
+    <column index="4" property="HireDate"/>
+    <column index="5" property="Salary"/>
+    <column index="6" property="IsActive"/>
+    <column index="7" property="Status"/>
+  </sheet>
+</columnMetadata>
 </file>
--- a/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
+++ b/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
@@ -137,7 +137,7 @@
         <f>A2 * 10000</f>
       </c>
       <c r="F2" s="2" t="b">
-        <v>true</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -166,7 +166,7 @@
         <f>A3 * 10000</f>
       </c>
       <c r="F3" s="2" t="b">
-        <v>true</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -195,7 +195,7 @@
         <f>A4 * 10000</f>
       </c>
       <c r="F4" s="2" t="b">
-        <v>false</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -224,7 +224,7 @@
         <f>A5 * 10000</f>
       </c>
       <c r="F5" s="2" t="b">
-        <v>true</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>

--- a/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
+++ b/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -41,7 +41,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
     <xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
     <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyAlignment="1">
@@ -53,7 +53,17 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0"/>
   </cellXfs>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -64,7 +74,7 @@
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="5" max="5" width="17" style="5" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
@@ -127,7 +137,7 @@
         <f>A2 * 10000</f>
       </c>
       <c r="F2" s="2" t="b">
-        <v>true</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -156,7 +166,7 @@
         <f>A3 * 10000</f>
       </c>
       <c r="F3" s="2" t="b">
-        <v>true</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -185,7 +195,7 @@
         <f>A4 * 10000</f>
       </c>
       <c r="F4" s="2" t="b">
-        <v>false</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -214,7 +224,7 @@
         <f>A5 * 10000</f>
       </c>
       <c r="F5" s="2" t="b">
-        <v>true</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -224,5 +234,51 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G5"/>
+  <conditionalFormatting sqref="A2:A5">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(A2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B5">
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(B2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C5">
+    <cfRule type="containsBlanks" dxfId="0" priority="3">
+      <formula>LEN(TRIM(C2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="5">
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="A2:A5">
+      <formula1>ISNUMBER(A2)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="B2:B5">
+      <formula1>LEN(TRIM(B2))&gt;0</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="C2:C5">
+      <formula1>LEN(TRIM(C2))&gt;0</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="F2:F5">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." sqref="G2:G5">
+      <formula1>"Full Time,Part Time,Contract,Terminated"</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Sheet1">
+    <column index="1" property="Id"/>
+    <column index="2" property="Name"/>
+    <column index="3" property="Email"/>
+    <column index="4" property="HireDate"/>
+    <column index="5" property="Salary"/>
+    <column index="6" property="IsActive"/>
+    <column index="7" property="Status"/>
+  </sheet>
+</columnMetadata>
 </file>
--- a/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
+++ b/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
@@ -73,7 +73,7 @@
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="17" style="5" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>

--- a/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
+++ b/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
@@ -70,11 +70,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="17" style="5" customWidth="1"/>
+    <col min="5" max="5" width="18" style="5" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>

--- a/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
+++ b/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
@@ -74,7 +74,7 @@
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="18" style="5" customWidth="1"/>
+    <col min="5" max="5" width="15" style="5" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>

--- a/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
+++ b/src/Excelsior.Tests/FormulaTests.Fluent.verified.xlsx
@@ -70,11 +70,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="17" style="5" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="15" style="5" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
